--- a/Einwagen.xlsx
+++ b/Einwagen.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="W:\Laufende_Projekte\Project_PGE\PGE_ID_conc_calc\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="W:\Laufende_Projekte\Project_PGE\PGE_ID\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95203AAF-B10F-40D8-8FBF-C08B69A04868}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{851CC684-A862-4D3F-8FCA-A245C4B6B178}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11925" xr2:uid="{DFAE9E4B-DED2-4D02-9538-14C27B848607}"/>
   </bookViews>
@@ -26,25 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
-  <si>
-    <t>Spike 1</t>
-  </si>
-  <si>
-    <t>Spike 2</t>
-  </si>
-  <si>
-    <t>Calib_Spike_1-2</t>
-  </si>
-  <si>
-    <t>Calib_Spike_2-2</t>
-  </si>
-  <si>
-    <t>Calib_Spike_3-2</t>
-  </si>
-  <si>
-    <t>Calib_Spike_4-2</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
   <si>
     <t>date</t>
   </si>
@@ -59,6 +41,33 @@
   </si>
   <si>
     <t>EW_gesamt</t>
+  </si>
+  <si>
+    <t>Calib_1</t>
+  </si>
+  <si>
+    <t>Calib_Spike_1</t>
+  </si>
+  <si>
+    <t>Calib_Spike_2</t>
+  </si>
+  <si>
+    <t>Calib_Spike_3</t>
+  </si>
+  <si>
+    <t>Calib_Spike_4</t>
+  </si>
+  <si>
+    <t>Calib_2</t>
+  </si>
+  <si>
+    <t>Calib_3</t>
+  </si>
+  <si>
+    <t>Spike_1</t>
+  </si>
+  <si>
+    <t>Spike_2</t>
   </si>
 </sst>
 </file>
@@ -428,7 +437,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{80C9BD48-CD22-4E0E-8F4B-88C629425627}">
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="25.85546875" style="1" customWidth="1"/>
@@ -437,27 +446,27 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="B2" s="3">
-        <v>45194</v>
+        <v>45176</v>
       </c>
       <c r="D2" s="1">
         <v>1.0078</v>
@@ -470,10 +479,10 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="B3" s="3">
-        <v>45195</v>
+        <v>45176</v>
       </c>
       <c r="D3" s="1">
         <v>1.0105</v>
@@ -484,10 +493,10 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="B4" s="3">
-        <v>45196</v>
+        <v>45176</v>
       </c>
       <c r="C4" s="1">
         <v>1.0039</v>
@@ -501,10 +510,10 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="B5" s="3">
-        <v>45197</v>
+        <v>45176</v>
       </c>
       <c r="C5" s="1">
         <v>1.0039</v>
@@ -518,10 +527,10 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="B6" s="3">
-        <v>45198</v>
+        <v>45176</v>
       </c>
       <c r="C6" s="1">
         <v>1.0047999999999999</v>
@@ -535,10 +544,10 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B7" s="3">
-        <v>45199</v>
+        <v>45176</v>
       </c>
       <c r="C7" s="1">
         <v>1.0033000000000001</v>
@@ -548,6 +557,48 @@
       </c>
       <c r="E7" s="1">
         <v>10.0342</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B8" s="3">
+        <v>45176</v>
+      </c>
+      <c r="C8" s="1">
+        <v>1.004</v>
+      </c>
+      <c r="E8" s="1">
+        <v>10.044700000000001</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" s="3">
+        <v>45176</v>
+      </c>
+      <c r="C9" s="1">
+        <v>1.0037</v>
+      </c>
+      <c r="E9" s="1">
+        <v>10.0381</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" s="3">
+        <v>45176</v>
+      </c>
+      <c r="C10" s="1">
+        <v>1.0073000000000001</v>
+      </c>
+      <c r="E10" s="1">
+        <v>10.0328</v>
       </c>
     </row>
   </sheetData>

--- a/Einwagen.xlsx
+++ b/Einwagen.xlsx
@@ -1,22 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20402"/>
-  <workbookPr defaultThemeVersion="166925"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="W:\Laufende_Projekte\Project_PGE\PGE_ID\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\J\Desktop\PGE_ID\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{851CC684-A862-4D3F-8FCA-A245C4B6B178}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11925" xr2:uid="{DFAE9E4B-DED2-4D02-9538-14C27B848607}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11928"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
     <sheet name="Tabelle2" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="152511"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -26,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="28">
   <si>
     <t>date</t>
   </si>
@@ -68,12 +67,54 @@
   </si>
   <si>
     <t>Spike_2</t>
+  </si>
+  <si>
+    <t>Spike_3</t>
+  </si>
+  <si>
+    <t>Spike_4</t>
+  </si>
+  <si>
+    <t>HCl+Spike_1</t>
+  </si>
+  <si>
+    <t>BCR-2_(1026)</t>
+  </si>
+  <si>
+    <t>BHVO-2_(1026)</t>
+  </si>
+  <si>
+    <t>SPS_SW2_1</t>
+  </si>
+  <si>
+    <t>Tiefensee_Evap_1</t>
+  </si>
+  <si>
+    <t>Tiefensee+Spike_1</t>
+  </si>
+  <si>
+    <t>T248_(9823)_1</t>
+  </si>
+  <si>
+    <t>T225_(3719)_1</t>
+  </si>
+  <si>
+    <t>Blank+Spike_EV_1</t>
+  </si>
+  <si>
+    <t>Blank_HCl_nospike_1</t>
+  </si>
+  <si>
+    <t>0.1_ppb+Spike_1</t>
+  </si>
+  <si>
+    <t>1_ppb+Spike_1</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -436,15 +477,15 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{80C9BD48-CD22-4E0E-8F4B-88C629425627}">
-  <dimension ref="A1:G10"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:G26"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="25.85546875" style="1" customWidth="1"/>
-    <col min="2" max="16384" width="11.42578125" style="1"/>
+    <col min="1" max="1" width="25.88671875" style="1" customWidth="1"/>
+    <col min="2" max="16384" width="11.44140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -461,7 +502,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>12</v>
       </c>
@@ -477,7 +518,7 @@
       <c r="F2" s="3"/>
       <c r="G2" s="3"/>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>13</v>
       </c>
@@ -491,7 +532,7 @@
         <v>10.0511</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
@@ -508,7 +549,7 @@
         <v>10.049200000000001</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>7</v>
       </c>
@@ -525,7 +566,7 @@
         <v>10.0488</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>8</v>
       </c>
@@ -542,7 +583,7 @@
         <v>10.060700000000001</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>9</v>
       </c>
@@ -559,7 +600,7 @@
         <v>10.0342</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>5</v>
       </c>
@@ -573,7 +614,7 @@
         <v>10.044700000000001</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>10</v>
       </c>
@@ -587,7 +628,7 @@
         <v>10.0381</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>11</v>
       </c>
@@ -599,6 +640,260 @@
       </c>
       <c r="E10" s="1">
         <v>10.0328</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B11" s="3">
+        <v>45173</v>
+      </c>
+      <c r="D11" s="1">
+        <v>0.1007</v>
+      </c>
+      <c r="E11" s="1">
+        <v>10.008599999999999</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A12" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B12" s="3">
+        <v>45173</v>
+      </c>
+      <c r="D12" s="1">
+        <v>0.1003</v>
+      </c>
+      <c r="E12" s="1">
+        <v>10.0124</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A13" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B13" s="3">
+        <v>45173</v>
+      </c>
+      <c r="D13" s="1">
+        <v>9.7999999999999997E-3</v>
+      </c>
+      <c r="E13" s="1">
+        <v>10.001300000000001</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A14" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B14" s="3">
+        <v>45173</v>
+      </c>
+      <c r="D14" s="1">
+        <v>1.24E-2</v>
+      </c>
+      <c r="E14" s="1">
+        <v>9.9176000000000002</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A15" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B15" s="3">
+        <v>45173</v>
+      </c>
+      <c r="D15" s="1">
+        <v>9.9599999999999994E-2</v>
+      </c>
+      <c r="E15" s="1">
+        <v>9.8729999999999993</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A16" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B16" s="3">
+        <v>45173</v>
+      </c>
+      <c r="C16" s="1">
+        <v>32.220300000000002</v>
+      </c>
+      <c r="D16" s="1">
+        <v>0.1003</v>
+      </c>
+      <c r="E16" s="1">
+        <v>9.8879000000000001</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A17" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B17" s="3">
+        <v>45173</v>
+      </c>
+      <c r="C17" s="1">
+        <v>31.165199999999999</v>
+      </c>
+      <c r="E17" s="1">
+        <v>10.096500000000001</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A18" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B18" s="3">
+        <v>45173</v>
+      </c>
+      <c r="C18" s="1">
+        <v>31.0886</v>
+      </c>
+      <c r="D18" s="1">
+        <v>9.8699999999999996E-2</v>
+      </c>
+      <c r="E18" s="1">
+        <v>9.6114999999999995</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A19" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B19" s="3">
+        <v>45173</v>
+      </c>
+      <c r="C19" s="1">
+        <v>1.0084</v>
+      </c>
+      <c r="D19" s="1">
+        <v>9.98E-2</v>
+      </c>
+      <c r="E19" s="1">
+        <v>10.019500000000001</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A20" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B20" s="3">
+        <v>45173</v>
+      </c>
+      <c r="C20" s="1">
+        <v>1.0087999999999999</v>
+      </c>
+      <c r="D20" s="1">
+        <v>9.9900000000000003E-2</v>
+      </c>
+      <c r="E20" s="1">
+        <v>10.0481</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A21" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B21" s="3">
+        <v>45173</v>
+      </c>
+      <c r="C21" s="1">
+        <v>8.6513000000000009</v>
+      </c>
+      <c r="D21" s="1">
+        <v>0.10009999999999999</v>
+      </c>
+      <c r="E21" s="1">
+        <v>8.7513000000000005</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A22" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B22" s="3">
+        <v>45173</v>
+      </c>
+      <c r="C22" s="1">
+        <v>10.6534</v>
+      </c>
+      <c r="D22" s="1">
+        <v>9.8500000000000004E-2</v>
+      </c>
+      <c r="E22" s="1">
+        <v>10.661899999999999</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A23" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B23" s="3">
+        <v>45173</v>
+      </c>
+      <c r="C23" s="1">
+        <v>9.7995999999999999</v>
+      </c>
+      <c r="D23" s="1">
+        <v>9.8599999999999993E-2</v>
+      </c>
+      <c r="E23" s="1">
+        <v>9.8981999999999992</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A24" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B24" s="3">
+        <v>45173</v>
+      </c>
+      <c r="C24" s="1">
+        <v>9.7626000000000008</v>
+      </c>
+      <c r="D24" s="1">
+        <v>0.10249999999999999</v>
+      </c>
+      <c r="E24" s="1">
+        <v>9.8651</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A25" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B25" s="3">
+        <v>45173</v>
+      </c>
+      <c r="C25" s="1">
+        <v>9.2999999999999992E-3</v>
+      </c>
+      <c r="D25" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="E25" s="1">
+        <v>10.0054</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A26" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B26" s="3">
+        <v>45173</v>
+      </c>
+      <c r="C26" s="1">
+        <v>9.8699999999999996E-2</v>
+      </c>
+      <c r="D26" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="E26" s="1">
+        <v>10.005800000000001</v>
       </c>
     </row>
   </sheetData>
@@ -607,9 +902,9 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{547BC729-B26D-4538-A49B-529ED6A7389C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
